--- a/Team-Data/2014-15/12-29-2014-15.xlsx
+++ b/Team-Data/2014-15/12-29-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>4.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>4</v>
@@ -760,7 +827,7 @@
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL2" t="n">
         <v>7</v>
@@ -787,22 +854,22 @@
         <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
         <v>3</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -927,7 +994,7 @@
         <v>23</v>
       </c>
       <c r="AF3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
         <v>22</v>
@@ -939,10 +1006,10 @@
         <v>3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
@@ -957,10 +1024,10 @@
         <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>19</v>
@@ -984,16 +1051,16 @@
         <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
         <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>0.467</v>
+        <v>0.448</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
@@ -1043,7 +1110,7 @@
         <v>36.4</v>
       </c>
       <c r="J4" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K4" t="n">
         <v>0.447</v>
@@ -1055,67 +1122,67 @@
         <v>21.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.336</v>
+        <v>0.335</v>
       </c>
       <c r="O4" t="n">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
       <c r="P4" t="n">
-        <v>22.7</v>
+        <v>22.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.746</v>
+        <v>0.749</v>
       </c>
       <c r="R4" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T4" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U4" t="n">
         <v>20.8</v>
       </c>
       <c r="V4" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="W4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
         <v>4.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z4" t="n">
         <v>20.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.8</v>
+        <v>96.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.3</v>
+        <v>-2.7</v>
       </c>
       <c r="AD4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE4" t="n">
         <v>18</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>16</v>
       </c>
       <c r="AF4" t="n">
         <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="n">
         <v>24</v>
@@ -1127,52 +1194,52 @@
         <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AM4" t="n">
         <v>17</v>
       </c>
       <c r="AN4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO4" t="n">
         <v>22</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>21</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AQ4" t="n">
         <v>18</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>17</v>
       </c>
       <c r="AR4" t="n">
         <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU4" t="n">
         <v>18</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BB4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -1207,106 +1274,106 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>0.313</v>
+        <v>0.323</v>
       </c>
       <c r="H5" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="I5" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J5" t="n">
-        <v>85.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.428</v>
+        <v>0.43</v>
       </c>
       <c r="L5" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.322</v>
+        <v>0.324</v>
       </c>
       <c r="O5" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P5" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.737</v>
+        <v>0.734</v>
       </c>
       <c r="R5" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="T5" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="U5" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V5" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="W5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="X5" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
         <v>95.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4.7</v>
+        <v>-4.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG5" t="n">
         <v>25</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL5" t="n">
         <v>26</v>
@@ -1324,16 +1391,16 @@
         <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR5" t="n">
         <v>26</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU5" t="n">
         <v>23</v>
@@ -1342,25 +1409,25 @@
         <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB5" t="n">
         <v>24</v>
       </c>
       <c r="BC5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -1389,106 +1456,106 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
         <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.455</v>
+        <v>0.458</v>
       </c>
       <c r="L6" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="N6" t="n">
         <v>0.365</v>
       </c>
       <c r="O6" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="P6" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.781</v>
+        <v>0.777</v>
       </c>
       <c r="R6" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S6" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="T6" t="n">
         <v>45.5</v>
       </c>
       <c r="U6" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="V6" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="X6" t="n">
         <v>6.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>103.1</v>
+        <v>103.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AD6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH6" t="n">
         <v>11</v>
       </c>
-      <c r="AE6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>13</v>
-      </c>
       <c r="AI6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ6" t="n">
         <v>22</v>
       </c>
       <c r="AK6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AL6" t="n">
         <v>14</v>
@@ -1506,13 +1573,13 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT6" t="n">
         <v>4</v>
@@ -1521,16 +1588,16 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX6" t="n">
         <v>2</v>
       </c>
       <c r="AY6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ6" t="n">
         <v>5</v>
@@ -1539,10 +1606,10 @@
         <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>2.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1670,7 +1737,7 @@
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL7" t="n">
         <v>11</v>
@@ -1679,13 +1746,13 @@
         <v>13</v>
       </c>
       <c r="AN7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
         <v>5</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
         <v>12</v>
@@ -1694,10 +1761,10 @@
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU7" t="n">
         <v>9</v>
@@ -1706,19 +1773,19 @@
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -1753,97 +1820,97 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
         <v>22</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.71</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="J8" t="n">
-        <v>86.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L8" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O8" t="n">
         <v>17.9</v>
       </c>
       <c r="P8" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.764</v>
+        <v>0.766</v>
       </c>
       <c r="R8" t="n">
         <v>11.2</v>
       </c>
       <c r="S8" t="n">
-        <v>31.2</v>
+        <v>30.9</v>
       </c>
       <c r="T8" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="V8" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="W8" t="n">
         <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>109.8</v>
+        <v>109.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>1</v>
@@ -1864,22 +1931,22 @@
         <v>16</v>
       </c>
       <c r="AO8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP8" t="n">
         <v>15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
         <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -1897,7 +1964,7 @@
         <v>2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>-2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH9" t="n">
         <v>13</v>
@@ -2049,7 +2116,7 @@
         <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
         <v>20</v>
@@ -2067,13 +2134,13 @@
         <v>19</v>
       </c>
       <c r="AV9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW9" t="n">
         <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY9" t="n">
         <v>27</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>27</v>
@@ -2207,10 +2274,10 @@
         <v>27</v>
       </c>
       <c r="AH10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ10" t="n">
         <v>7</v>
@@ -2240,13 +2307,13 @@
         <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
@@ -2255,7 +2322,7 @@
         <v>18</v>
       </c>
       <c r="AX10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2410,13 +2477,13 @@
         <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP11" t="n">
         <v>25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR11" t="n">
         <v>23</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -2484,94 +2551,94 @@
         <v>29</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.724</v>
       </c>
       <c r="H12" t="n">
         <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="J12" t="n">
-        <v>82.7</v>
+        <v>82.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.43</v>
+        <v>0.428</v>
       </c>
       <c r="L12" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="M12" t="n">
         <v>34.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
       <c r="O12" t="n">
-        <v>18</v>
+        <v>18.7</v>
       </c>
       <c r="P12" t="n">
-        <v>25.4</v>
+        <v>26.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.709</v>
+        <v>0.71</v>
       </c>
       <c r="R12" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S12" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="T12" t="n">
-        <v>44.4</v>
+        <v>44.8</v>
       </c>
       <c r="U12" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V12" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="W12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="n">
         <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.7</v>
+        <v>100.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI12" t="n">
         <v>28</v>
@@ -2580,7 +2647,7 @@
         <v>18</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2604,31 +2671,31 @@
         <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
         <v>17</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -2663,22 +2730,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" t="n">
         <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>0.344</v>
+        <v>0.355</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J13" t="n">
         <v>84.3</v>
@@ -2687,34 +2754,34 @@
         <v>0.431</v>
       </c>
       <c r="L13" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M13" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O13" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="P13" t="n">
         <v>20.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.729</v>
+        <v>0.732</v>
       </c>
       <c r="R13" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S13" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="T13" t="n">
         <v>45.3</v>
       </c>
       <c r="U13" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V13" t="n">
         <v>14.3</v>
@@ -2723,31 +2790,31 @@
         <v>5.7</v>
       </c>
       <c r="X13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y13" t="n">
         <v>4.8</v>
       </c>
-      <c r="Y13" t="n">
-        <v>4.9</v>
-      </c>
       <c r="Z13" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.5</v>
+        <v>94.7</v>
       </c>
       <c r="AC13" t="n">
         <v>-1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
       </c>
       <c r="AF13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
         <v>23</v>
@@ -2765,7 +2832,7 @@
         <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2777,43 +2844,43 @@
         <v>28</v>
       </c>
       <c r="AP13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR13" t="n">
         <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
         <v>5</v>
       </c>
       <c r="AU13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ13" t="n">
         <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
         <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>0.656</v>
+        <v>0.645</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2872,61 +2939,61 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.385</v>
+        <v>0.383</v>
       </c>
       <c r="O14" t="n">
         <v>19</v>
       </c>
       <c r="P14" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="S14" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
         <v>40.6</v>
       </c>
       <c r="U14" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="V14" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W14" t="n">
         <v>7.7</v>
       </c>
       <c r="X14" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Y14" t="n">
         <v>3.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA14" t="n">
         <v>22.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.1</v>
+        <v>106.3</v>
       </c>
       <c r="AC14" t="n">
         <v>5.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF14" t="n">
         <v>10</v>
@@ -2959,19 +3026,19 @@
         <v>6</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
       </c>
       <c r="AS14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU14" t="n">
         <v>6</v>
@@ -2983,13 +3050,13 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -3027,121 +3094,121 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" t="n">
         <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>38.5</v>
+        <v>38.1</v>
       </c>
       <c r="J15" t="n">
-        <v>87.7</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.439</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M15" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O15" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S15" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="T15" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="V15" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="W15" t="n">
         <v>7.6</v>
       </c>
       <c r="X15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.7</v>
+        <v>102.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI15" t="n">
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK15" t="n">
         <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM15" t="n">
         <v>21</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ15" t="n">
         <v>19</v>
@@ -3153,19 +3220,19 @@
         <v>24</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW15" t="n">
         <v>14</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
         <v>7</v>
@@ -3174,13 +3241,13 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BB15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3320,49 +3387,49 @@
         <v>14</v>
       </c>
       <c r="AO16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP16" t="n">
         <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX16" t="n">
         <v>25</v>
       </c>
       <c r="AY16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -3391,52 +3458,52 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" t="n">
         <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>0.438</v>
+        <v>0.452</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="J17" t="n">
-        <v>74.3</v>
+        <v>74.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L17" t="n">
         <v>7.8</v>
       </c>
       <c r="M17" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.359</v>
+        <v>0.356</v>
       </c>
       <c r="O17" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="P17" t="n">
-        <v>24.7</v>
+        <v>24.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="T17" t="n">
         <v>35.9</v>
@@ -3454,31 +3521,31 @@
         <v>3.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.7</v>
+        <v>94.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.2</v>
+        <v>-3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH17" t="n">
         <v>29</v>
@@ -3490,25 +3557,25 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN17" t="n">
         <v>13</v>
       </c>
-      <c r="AM17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>12</v>
-      </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3523,7 +3590,7 @@
         <v>29</v>
       </c>
       <c r="AV17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
         <v>6</v>
@@ -3532,16 +3599,16 @@
         <v>30</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC17" t="n">
         <v>22</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -3573,37 +3640,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.484</v>
       </c>
       <c r="H18" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J18" t="n">
-        <v>81.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K18" t="n">
         <v>0.464</v>
       </c>
       <c r="L18" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
         <v>19.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O18" t="n">
         <v>17.1</v>
@@ -3612,31 +3679,31 @@
         <v>21.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.78</v>
+        <v>0.778</v>
       </c>
       <c r="R18" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="S18" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="T18" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U18" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V18" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="W18" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z18" t="n">
         <v>23</v>
@@ -3645,13 +3712,13 @@
         <v>20.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3660,10 +3727,10 @@
         <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI18" t="n">
         <v>13</v>
@@ -3696,13 +3763,13 @@
         <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV18" t="n">
         <v>28</v>
@@ -3711,22 +3778,22 @@
         <v>4</v>
       </c>
       <c r="AX18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
         <v>19</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-10.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3848,10 +3915,10 @@
         <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3863,7 +3930,7 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO19" t="n">
         <v>4</v>
@@ -3890,13 +3957,13 @@
         <v>25</v>
       </c>
       <c r="AW19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX19" t="n">
         <v>21</v>
       </c>
       <c r="AY19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ19" t="n">
         <v>15</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -3937,106 +4004,106 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
         <v>15</v>
       </c>
       <c r="G20" t="n">
-        <v>0.483</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J20" t="n">
-        <v>84.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.337</v>
+        <v>0.334</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.756</v>
       </c>
       <c r="R20" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="T20" t="n">
-        <v>42.2</v>
+        <v>42.9</v>
       </c>
       <c r="U20" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V20" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="W20" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
         <v>101.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1</v>
+        <v>-0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
         <v>8</v>
       </c>
       <c r="AJ20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -4045,43 +4112,43 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -4251,10 +4318,10 @@
         <v>15</v>
       </c>
       <c r="AV21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW21" t="n">
         <v>19</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>20</v>
       </c>
       <c r="AX21" t="n">
         <v>27</v>
@@ -4263,7 +4330,7 @@
         <v>4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA21" t="n">
         <v>25</v>
@@ -4272,7 +4339,7 @@
         <v>27</v>
       </c>
       <c r="BC21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4449,7 @@
         <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF22" t="n">
         <v>17</v>
@@ -4391,10 +4458,10 @@
         <v>16</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ22" t="n">
         <v>16</v>
@@ -4406,7 +4473,7 @@
         <v>20</v>
       </c>
       <c r="AM22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN22" t="n">
         <v>27</v>
@@ -4418,7 +4485,7 @@
         <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR22" t="n">
         <v>6</v>
@@ -4436,13 +4503,13 @@
         <v>24</v>
       </c>
       <c r="AW22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ22" t="n">
         <v>27</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -4486,67 +4553,67 @@
         <v>33</v>
       </c>
       <c r="E23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>0.394</v>
+        <v>0.364</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J23" t="n">
-        <v>80.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.1</v>
+        <v>18.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.38</v>
+        <v>0.377</v>
       </c>
       <c r="O23" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="P23" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.721</v>
+        <v>0.723</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>32.2</v>
       </c>
       <c r="T23" t="n">
-        <v>40.4</v>
+        <v>41</v>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="Z23" t="n">
         <v>20.8</v>
@@ -4555,19 +4622,19 @@
         <v>18.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-4.5</v>
+        <v>-5.1</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG23" t="n">
         <v>21</v>
@@ -4576,22 +4643,22 @@
         <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="n">
         <v>26</v>
       </c>
       <c r="AN23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4606,25 +4673,25 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AT23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU23" t="n">
         <v>28</v>
       </c>
-      <c r="AU23" t="n">
-        <v>26</v>
-      </c>
       <c r="AV23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX23" t="n">
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>16</v>
@@ -4636,7 +4703,7 @@
         <v>29</v>
       </c>
       <c r="BC23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE24" t="n">
         <v>30</v>
@@ -4767,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AM24" t="n">
         <v>10</v>
@@ -4776,25 +4843,25 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS24" t="n">
         <v>22</v>
       </c>
       <c r="AT24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,10 +4870,10 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4995,7 @@
         <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF25" t="n">
         <v>13</v>
@@ -4937,16 +5004,16 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ25" t="n">
         <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL25" t="n">
         <v>2</v>
@@ -4967,7 +5034,7 @@
         <v>1</v>
       </c>
       <c r="AR25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
         <v>19</v>
@@ -4985,7 +5052,7 @@
         <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -5122,13 +5189,13 @@
         <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ26" t="n">
         <v>4</v>
       </c>
       <c r="AK26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
@@ -5149,7 +5216,7 @@
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
         <v>26</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E27" t="n">
         <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G27" t="n">
-        <v>0.419</v>
+        <v>0.433</v>
       </c>
       <c r="H27" t="n">
         <v>48.8</v>
@@ -5229,25 +5296,25 @@
         <v>36.6</v>
       </c>
       <c r="J27" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="K27" t="n">
         <v>0.461</v>
       </c>
       <c r="L27" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M27" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.347</v>
+        <v>0.343</v>
       </c>
       <c r="O27" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="P27" t="n">
-        <v>30.9</v>
+        <v>31.2</v>
       </c>
       <c r="Q27" t="n">
         <v>0.775</v>
@@ -5259,49 +5326,49 @@
         <v>33.4</v>
       </c>
       <c r="T27" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U27" t="n">
         <v>20</v>
       </c>
       <c r="V27" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="W27" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X27" t="n">
         <v>3.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="AB27" t="n">
-        <v>102.5</v>
+        <v>102.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG27" t="n">
         <v>19</v>
       </c>
       <c r="AH27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI27" t="n">
         <v>22</v>
@@ -5319,7 +5386,7 @@
         <v>29</v>
       </c>
       <c r="AN27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5337,10 +5404,10 @@
         <v>7</v>
       </c>
       <c r="AT27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
@@ -5355,13 +5422,13 @@
         <v>30</v>
       </c>
       <c r="AZ27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC27" t="n">
         <v>18</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F28" t="n">
         <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>0.581</v>
+        <v>0.594</v>
       </c>
       <c r="H28" t="n">
         <v>49.3</v>
@@ -5411,43 +5478,43 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.465</v>
+        <v>0.467</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="N28" t="n">
-        <v>0.377</v>
+        <v>0.382</v>
       </c>
       <c r="O28" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P28" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R28" t="n">
         <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="T28" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="U28" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="V28" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W28" t="n">
         <v>7.5</v>
@@ -5465,13 +5532,13 @@
         <v>20.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.9</v>
+        <v>102.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5492,7 +5559,7 @@
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL28" t="n">
         <v>9</v>
@@ -5501,16 +5568,16 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP28" t="n">
         <v>17</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>24</v>
@@ -5525,22 +5592,22 @@
         <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX28" t="n">
         <v>6</v>
       </c>
       <c r="AY28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB28" t="n">
         <v>9</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>8.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5689,13 +5756,13 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ29" t="n">
         <v>4</v>
       </c>
       <c r="AR29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E30" t="n">
         <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>0.323</v>
+        <v>0.333</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
@@ -5775,10 +5842,10 @@
         <v>35.8</v>
       </c>
       <c r="J30" t="n">
-        <v>78.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L30" t="n">
         <v>6.8</v>
@@ -5787,31 +5854,31 @@
         <v>20.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.333</v>
+        <v>0.33</v>
       </c>
       <c r="O30" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="P30" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.744</v>
+        <v>0.749</v>
       </c>
       <c r="R30" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="S30" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T30" t="n">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="U30" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="V30" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W30" t="n">
         <v>6.2</v>
@@ -5820,13 +5887,13 @@
         <v>5.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB30" t="n">
         <v>96.09999999999999</v>
@@ -5835,13 +5902,13 @@
         <v>-4.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
       </c>
       <c r="AF30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG30" t="n">
         <v>24</v>
@@ -5850,13 +5917,13 @@
         <v>29</v>
       </c>
       <c r="AI30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ30" t="n">
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5865,25 +5932,25 @@
         <v>20</v>
       </c>
       <c r="AN30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP30" t="n">
         <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU30" t="n">
         <v>24</v>
@@ -5898,7 +5965,7 @@
         <v>7</v>
       </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ30" t="n">
         <v>4</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.733</v>
+        <v>0.724</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J31" t="n">
-        <v>83</v>
+        <v>83.3</v>
       </c>
       <c r="K31" t="n">
         <v>0.472</v>
@@ -5969,70 +6036,70 @@
         <v>15.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.392</v>
+        <v>0.39</v>
       </c>
       <c r="O31" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="P31" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.74</v>
+        <v>0.732</v>
       </c>
       <c r="R31" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="T31" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="U31" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="V31" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="W31" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA31" t="n">
         <v>20.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF31" t="n">
         <v>4</v>
       </c>
       <c r="AG31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH31" t="n">
         <v>10</v>
       </c>
       <c r="AI31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ31" t="n">
         <v>15</v>
@@ -6056,10 +6123,10 @@
         <v>23</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS31" t="n">
         <v>10</v>
@@ -6071,22 +6138,22 @@
         <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX31" t="n">
         <v>10</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
         <v>21</v>
       </c>
       <c r="BA31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-29-2014-15</t>
+          <t>2014-12-29</t>
         </is>
       </c>
     </row>
